--- a/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.03075753</t>
+          <t>-5.85579333</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.96898339</t>
+          <t>-77.24328833</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CONSULTORIO MEDICO FLAFER</t>
+          <t>PUESTO DE SALUD ATUMPLAYA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA NUMERO 525 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>OTROS CAS. ATUMPLAYA S-N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.0354138</t>
+          <t>-6.0419882</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9704225</t>
+          <t>-76.9700669</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CONSULTORIO DERMATOLOGICO DERMAPIEL</t>
+          <t>PUESTO DE SALUD DEL E.P. SAN CRISTOBAL MOYOBAMBA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CALLAO NUMERO 353 A PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>PROLONGACION PROLONGACION 25 DE MAYO - SECTOR SHANGO PARTE ALTA BARRIO BELAN - MOYOBAMBA DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>35887</t>
+          <t>18077</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,32 +642,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.0334985</t>
+          <t>-6.0441596</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9619848</t>
+          <t>-76.971282</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO CORA</t>
+          <t>POLICLINICO POLICIAL MOYOBAMBA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JESUS ALBERTO MIRANDA NUMERO 251 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>AVENIDA AV. GRAU 451 BARRIO DE CALVARIO DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,27 +704,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.03439643</t>
+          <t>-6.0421468</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.97795642</t>
+          <t>-76.97831239</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO ALPHADENT</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO MOYOBAMBA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EMILIO ACOSTA NUMERO 546 PISO 2 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>Los Caimitos NUMERO SIN NUMERO URBANIZACION Barrio El Belen DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,27 +766,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.036998</t>
+          <t>-5.95419654</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9759954</t>
+          <t>-76.91412962</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO WORK MEDIC</t>
+          <t>PUESTO DE SALUD SUGLLAQUIRO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OTROS CONJUNTO HABITACIONAL FONAVI I MANZANA E LOTE 10 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. ALFONSO UGARTE S/N, CENTRO POBLADO SUGLLAQUIRO S/N JR. ALFONSO UGARTE S/N, CENTRO POBLADO SUGLLAQUIRO MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.0419882</t>
+          <t>-5.92506725</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9700669</t>
+          <t>-76.89924637</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Consultorio Odontologico PRO-DENTIST</t>
+          <t>PUESTO DE SALUD EL CONDOR</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JunA­n NUMERO 600 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>HUANCABAMBA NUMERO SN DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>220103</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -885,32 +885,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MOYOBAMBA</t>
+          <t>HABANA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.85579333</t>
+          <t>-6.08042667</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.24328833</t>
+          <t>-77.09056333</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ATUMPLAYA</t>
+          <t>CENTRO DE SALUD HABANA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OTROS CAS. ATUMPLAYA S-N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>AVENIDA AV. NICOLAS DE PIAROLA S/N NUMERO S/N DISTRITO HABANA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.0294357</t>
+          <t>-5.95680362</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.96769046</t>
+          <t>-76.8717844</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CONSULTORIO MEDICO PEDIATRICO DRA. CARO</t>
+          <t>LA FLOR DE LA PRIMAVERA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PEDRO PASCASIO NORIEGA NUMERO 783 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>AVENIDA AV. 23 DE SETIEMBRE S/N CAS FLOR DE PRIMAVERA NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.0419882</t>
+          <t>-5.69268599</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9700669</t>
+          <t>-77.32512771</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CONSULTORIO ESTOMATOLAGICO SONRIE</t>
+          <t>IMPERIO DE CACHIYACU</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DOS DE MAYO NUMERO 161 PISO 1 DEPARTAMENTO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>CPM IMPERIO CACHIYACU JR. BUEN SAMARITANO S/N NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.0419882</t>
+          <t>-5.99050538</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9700669</t>
+          <t>-76.88500341</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD DEL E.P. SAN CRISTOBAL MOYOBAMBA</t>
+          <t>CORDILLERA ANDINA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PROLONGACION PROLONGACION 25 DE MAYO - SECTOR SHANGO PARTE ALTA BARRIO BELAN - MOYOBAMBA DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. ATAHUALPA S/N CENTRO POBLADO CORDILLERA ANDINA S/N JR. ATAHUALPA S/N CENTRO POBLADO CORDILLERA ANDINA MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.03287112</t>
+          <t>-5.75166333</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.97461181</t>
+          <t>-77.31414667</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO RAFAEL</t>
+          <t>DORADA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SERAFIN FILOMENO NUMERO 592 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. COCAMILLA S/N CAS. COMUNID.NATIVA LA DORADA S-N NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.04260168</t>
+          <t>-5.77632112</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.96929979</t>
+          <t>-77.23568746</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CONSULTORIO TERAPIA DEL DOLOR</t>
+          <t>RAFAEL BELAUNDE</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>URBANIZACION FONAVI I MANZANA D LOTE 11 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>CALLE CALLE SIMON BOLIVAR S/N CAS. RAFAEL BELAUNDE S-N NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.028632</t>
+          <t>-6.048488</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-76.9702109</t>
+          <t>-76.977125</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO "CM ODONTOLOGAA ESTATICA".</t>
+          <t>LA PRIMAVERA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PEDRO PASCASIO NORIEGA NUMERO 891 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>LOS CEDROS NUMERO S/N MANZANA A LOTE 15 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,27 +1324,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.0417671</t>
+          <t>-5.90585</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-76.9715703</t>
+          <t>-77.03900667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO VIRGEN DE LA PUERTA</t>
+          <t>CANABRAVA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20 DE ABRIL NUMERO 318 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR.ANGAIZA S/N CASERIO CANA BRAVA NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,32 +1386,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.0441596</t>
+          <t>-5.928445</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-76.971282</t>
+          <t>-77.01463333</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>POLICLINICO POLICIAL MOYOBAMBA</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AVENIDA AV. GRAU 451 BARRIO DE CALVARIO DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. 28  DE JULIO DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,27 +1448,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.0419882</t>
+          <t>-5.69228167</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-76.9700669</t>
+          <t>-77.37377167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CONSULTORIO MEDICO BUENA SALUD</t>
+          <t>SAN JOSE DE ALTO MAYO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AVENIDA AV. ALMIRANTE GRAU 201-B DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>OTROS CAS. SAN JOSE DEL ALTO MAYO S-N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,22 +1510,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.0300446</t>
+          <t>-5.80509667</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-76.9741302</t>
+          <t>-77.118035</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLAGICO  DRA SILVIA LOPEZ VELASQUEZ</t>
+          <t>NUEVA HUANCABAMBA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>JR. SAN MARTIN NÂ° 596 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. COMERCIO S/N - NUEVA HUANCABAMBA NUMERO S/N DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.04254033</t>
+          <t>-5.83055841</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-76.96806061</t>
+          <t>-77.0198989</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CELDENT CONSULTORIO DENTAL</t>
+          <t>MORROYACU</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>San Carlos NUMERO 198 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>OTROS CC.NN. MORROYACU DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,27 +1634,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.0421468</t>
+          <t>-5.84243167</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-76.97831239</t>
+          <t>-77.097665</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO MOYOBAMBA</t>
+          <t>SHIMPIYACU</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Los Caimitos NUMERO SIN NUMERO URBANIZACION Barrio El Belen DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>OTROS CC.NN. SHIMPIYACU DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,27 +1696,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.0321359</t>
+          <t>-5.93365642</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-76.9718826</t>
+          <t>-76.94277803</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CENTRO MADICO JOMA SALUD</t>
+          <t>QUILLOALLPA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ALONSO DE ALVARADO NUMERO 682 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>OTROS CENTRO POBLADO QUILLOALLPA CENTRO POBLADO QUILLOALLPA MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35641</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,27 +1758,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.0419058</t>
+          <t>-5.87476</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-76.9700099</t>
+          <t>-77.12019333</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO VMDENT</t>
+          <t>PUEBLO LIBRE</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Coronel Secada 166 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. 28 DE JULIO Nº 298 JR. 28 DE JULIO Nº 298 MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.04127914</t>
+          <t>-6.02317442</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-76.97161996</t>
+          <t>-76.9667939</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO BELESSA</t>
+          <t>TAHUISHCO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AMAZONAS MANZANA U LOTE 5 URBANIZACION VISTA ALEGRE DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
+          <t>JR. EDMUNDO DEL AGUILA S/N S/N JR. EDMUNDO DEL AGUILA S/N MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1849,1370 +1849,6 @@
         </is>
       </c>
       <c r="L23" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>15811</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-6.0330317</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-76.9747782</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLOGICO NOVADENT</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>JR. SAN MARTIN # 362 SEGUNDO PISO DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-6.0325139</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-76.9722734</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLAGICO DR. EDDY ANGULO VASQUEZ</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Jr.REYES GUERRA 487 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>6315</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-5.95419654</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-76.91412962</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD SUGLLAQUIRO</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>JR. ALFONSO UGARTE S/N, CENTRO POBLADO SUGLLAQUIRO S/N JR. ALFONSO UGARTE S/N, CENTRO POBLADO SUGLLAQUIRO MOYOBAMBA MOYOBAMBA SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>27097</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-5.92506725</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-76.89924637</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD EL CONDOR</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>HUANCABAMBA NUMERO SN DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>6327</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>220103</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>HABANA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-6.08042667</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-77.09056333</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CENTRO DE SALUD HABANA</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>AVENIDA AV. NICOLAS DE PIAROLA S/N NUMERO S/N DISTRITO HABANA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-6.03387622</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-76.96991177</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Serafin Filomeno NUMERO 184 PISO 2 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>14416</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-6.03143089</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-76.97352427</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>MEDICENTRO VILLARREAL</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>PEDRO CANGA NUMERO 547 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>35309</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-6.0295678</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-76.9832049</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>CONSULTORIO MEDICO SHALOM</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>APURIMAC NUMERO 1203 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>29610</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-6.0419882</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-76.9700669</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO SAN JUAN</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>ANDALUCIA NUMERO 604 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>18594</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-6.03633347</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-76.96921932</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DE LA MUJER</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>JR.CORONEL SECADA 275/ BARRIO DE CALVARIO DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>18346</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-6.040149</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-76.969729</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>CONSULTORIO OBSTETRICO JUAN PABLO II</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>JR. ANDALUCIA NÂ° 341 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33618</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-6.0414621</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-76.9694039</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>CONSULTORIO MEDICO TERAPAA DEL DOLOR</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>ANDALUCIA NUMERO 530 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-6.0324247</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-76.9744305</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLAGICO ODONTOLINAREZ</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>San MartA­n NUMERO 446 PISO 2 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>16301</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-6.0324623</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-76.9657486</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO SALDAAA</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>JR. LIBERTAD NÂ° 639 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>I-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>31827</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-6.0326132</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-76.9814741</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>CONSULTORIO MEDICO MADRE DE CRISTO</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28 DE JULIO NUMERO 219 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>34133</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-6.0339885</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-76.9699868</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>CONSULTORIO MEDICO GENITALE CLINIC</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>SERAFIN FILOMENO NUMERO 165 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-6.04752284</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-76.97729545</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Consultorio MA¨dico CardiolA²gico  Champi CA²rdova</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>URBANIZACION CONJUNTO HABITACINAL ALONSO DE ALVARADO MANZANA 4 LOTE 11 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>36583</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-6.03030526</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-76.97359669</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLAGICO SONRIMAX</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2 DE MAYO NUMERO 435 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>19255</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-6.0421296</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-76.9700336</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>POLICLINICO ALTO MAYO</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>AVENIDA AV. GRAU NÂ° 283 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-6.03280485</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-76.9742412</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLOGICO RAFAEL</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>JR. SERAFIN FILOMENO Nº 592 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>28032</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-6.02962775</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-76.96813571</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>CONSULTORIOS MADICOS "SAN MARCOS"</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20 DE ABRIL NUMERO 456 URBANIZACION ZARAGOZA DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>34531</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-6.0419882</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-76.9700669</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLOGICO K RITO DENT</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>SERAFIN FILOMENO NUMERO 186 PISO 1 DISTRITO MOYOBAMBA PROVINCIA MOYOBAMBA DEPARTAMENTO SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
         <is>
           <t>220101</t>
         </is>

--- a/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>6291</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-5.85579333</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>20825</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.0419882</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>18077</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.0441596</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>31275</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.0421468</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>6315</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-5.95419654</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>27097</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-5.92506725</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>6327</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>220103</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HABANA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.08042667</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>10110</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-5.95680362</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>6292</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-5.69268599</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>6707</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-5.99050538</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>6295</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-5.75166333</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>6293</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-5.77632112</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>31276</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-6.048488</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>6320</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-5.90585</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>6321</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-5.928445</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>6296</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-5.69228167</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>6325</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-5.80509667</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>6323</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-5.83055841</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>6324</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-5.84243167</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>6314</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-5.93365642</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-5.87476</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>6316</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-6.02317442</t>
@@ -1846,11 +1736,6 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/EstablecimientoSalud/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
